--- a/services/data_raw/eurostat/AT_coal_en_bal_nrg_bal_c.xlsx
+++ b/services/data_raw/eurostat/AT_coal_en_bal_nrg_bal_c.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,209 +417,209 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>freq</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>nrg_bal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>siec</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>geo\TIME_PERIOD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>1992</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>1993</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>1998</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -766,7 +754,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -901,7 +889,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1036,7 +1024,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1171,7 +1159,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1306,7 +1294,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1441,7 +1429,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1576,7 +1564,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1711,7 +1699,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1776,7 +1764,7 @@
       <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1911,7 +1899,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1976,7 +1964,7 @@
       <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2041,7 +2029,7 @@
       <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2106,7 +2094,7 @@
       <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2241,7 +2229,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2376,7 +2364,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2511,7 +2499,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2646,7 +2634,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2781,7 +2769,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2916,7 +2904,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -3051,7 +3039,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -3186,7 +3174,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -3251,7 +3239,7 @@
       <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -3316,7 +3304,7 @@
       <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -3381,7 +3369,7 @@
       <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -3446,7 +3434,7 @@
       <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -3511,7 +3499,7 @@
       <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -3646,7 +3634,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -3781,7 +3769,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -3916,7 +3904,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -3981,7 +3969,7 @@
       <c r="AO31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -4046,7 +4034,7 @@
       <c r="AO32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -4111,7 +4099,7 @@
       <c r="AO33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -4176,7 +4164,7 @@
       <c r="AO34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -4241,7 +4229,7 @@
       <c r="AO35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -4306,7 +4294,7 @@
       <c r="AO36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -4371,7 +4359,7 @@
       <c r="AO37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -4506,7 +4494,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -4641,7 +4629,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -4776,7 +4764,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -4841,7 +4829,7 @@
       <c r="AO41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -4906,7 +4894,7 @@
       <c r="AO42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -4971,7 +4959,7 @@
       <c r="AO43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -5036,7 +5024,7 @@
       <c r="AO44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -5171,7 +5159,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -5306,7 +5294,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -5371,7 +5359,7 @@
       <c r="AO47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -5436,7 +5424,7 @@
       <c r="AO48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -5501,7 +5489,7 @@
       <c r="AO49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -5566,7 +5554,7 @@
       <c r="AO50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -5631,7 +5619,7 @@
       <c r="AO51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -5696,7 +5684,7 @@
       <c r="AO52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -5761,7 +5749,7 @@
       <c r="AO53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -5826,7 +5814,7 @@
       <c r="AO54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -5891,7 +5879,7 @@
       <c r="AO55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -5956,7 +5944,7 @@
       <c r="AO56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -6021,7 +6009,7 @@
       <c r="AO57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -6156,7 +6144,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -6291,7 +6279,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -6426,7 +6414,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -6491,7 +6479,7 @@
       <c r="AO61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -6556,7 +6544,7 @@
       <c r="AO62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -6621,7 +6609,7 @@
       <c r="AO63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -6686,7 +6674,7 @@
       <c r="AO64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -6751,7 +6739,7 @@
       <c r="AO65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -6816,7 +6804,7 @@
       <c r="AO66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -6881,7 +6869,7 @@
       <c r="AO67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -7016,7 +7004,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -7151,7 +7139,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -7216,7 +7204,7 @@
       <c r="AO70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -7281,7 +7269,7 @@
       <c r="AO71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -7346,7 +7334,7 @@
       <c r="AO72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -7411,7 +7399,7 @@
       <c r="AO73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -7476,7 +7464,7 @@
       <c r="AO74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -7611,7 +7599,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -7746,7 +7734,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -7881,7 +7869,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -8016,7 +8004,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -8081,7 +8069,7 @@
       <c r="AO79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -8216,7 +8204,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -8351,7 +8339,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -8486,7 +8474,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -8621,7 +8609,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -8756,7 +8744,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -8891,7 +8879,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -8956,7 +8944,7 @@
       <c r="AO86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -9091,7 +9079,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -9156,7 +9144,7 @@
       <c r="AO88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -9221,7 +9209,7 @@
       <c r="AO89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -9286,7 +9274,7 @@
       <c r="AO90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -9351,7 +9339,7 @@
       <c r="AO91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -9486,7 +9474,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -9621,7 +9609,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -9756,7 +9744,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -9891,7 +9879,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -10026,7 +10014,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -10091,7 +10079,7 @@
       <c r="AO97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -10156,7 +10144,7 @@
       <c r="AO98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -10221,7 +10209,7 @@
       <c r="AO99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -10356,7 +10344,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -10491,7 +10479,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -10626,7 +10614,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" t="n">
         <v>101</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -10761,7 +10749,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -10896,7 +10884,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" t="n">
         <v>103</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -11031,7 +11019,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -11166,7 +11154,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" t="n">
         <v>105</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -11301,7 +11289,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" t="n">
         <v>106</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -11436,7 +11424,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" t="n">
         <v>107</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -11571,7 +11559,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -11706,7 +11694,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" t="n">
         <v>109</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -11841,7 +11829,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -11976,7 +11964,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -12111,7 +12099,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -12246,7 +12234,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -12381,7 +12369,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -12516,7 +12504,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -12651,7 +12639,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -12786,7 +12774,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -12851,7 +12839,7 @@
       <c r="AO119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -12916,7 +12904,7 @@
       <c r="AO120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -13051,7 +13039,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -13116,7 +13104,7 @@
       <c r="AO122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -13251,7 +13239,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -13386,7 +13374,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -13521,7 +13509,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -13656,7 +13644,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -13791,7 +13779,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -13926,7 +13914,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -14061,7 +14049,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -14196,7 +14184,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -14331,7 +14319,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -14466,7 +14454,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -14601,7 +14589,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -14736,7 +14724,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -14871,7 +14859,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -15006,7 +14994,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -15141,7 +15129,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -15276,7 +15264,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -15411,7 +15399,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="inlineStr">
